--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_946_Morocco_Central.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_946_Morocco_Central.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R649fcc8bc8d345f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9472bb7bed604bd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R49f54a3381dc4119"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R567e9684f4fb4886"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R0076dd439eac4d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb7292bc58484440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R953627cdab0c47f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R678f670a9f604e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R60a8dad9cdbf4695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R73b01da67c8140af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8c883b8451ad42cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8842973d4a1f4a86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ946CommercialTable" displayName="EEZ946CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ946CommercialTable" displayName="EEZ946CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ946FunctionalTable" displayName="EEZ946FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ946FunctionalTable" displayName="EEZ946FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ946ValidationTable" displayName="EEZ946ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ946ValidationTable" displayName="EEZ946ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -16238,7 +16192,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0a6e06bbaad4dbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45144e135f244fff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16248,20 +16202,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16269,714 +16213,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>9725.978124577001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>9725.978124577001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$233,A2,'Species'!$U$2:$U$233))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1252948.6958763546</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1252948.6958763546</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>4672.3729922721</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.333304360883963</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2154.290969191338</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>4672.3729922721</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2408.3973888903643</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$233,A3,'Species'!$U$2:$U$233))</x:f>
-        <x:v>11252930.914509986</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.333304360883963</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2154.290969191338</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>10065650.941945294</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1187279.9725646917</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1179536206264706</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1179536206264706</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>8553.3738722806</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1657040497037383</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>146.4549482499232</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>8553.3738722806</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>150.40665954426964</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$233,A4,'Species'!$U$2:$U$233))</x:f>
-        <x:v>1286484.3919629594</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1657040497037383</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>146.4549482499232</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1252683.9278271005</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>33800.46413585893</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0269824361796427</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.026982436179642737</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4604.1986899041995</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3968994226799336</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>249.4017076034804</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4604.1986899041995</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>271.76877148341083</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$233,A5,'Species'!$U$2:$U$233))</x:f>
-        <x:v>1251277.4216207939</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3968994226799336</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>249.4017076034804</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1148295.0154078146</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>102982.40621297923</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0896828818649928</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08968288186499289</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>471062.5948680407</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0605997927634006</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>114.9740401947342</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>471062.5948680407</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>115.00385760299632</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$233,A6,'Species'!$U$2:$U$233))</x:f>
-        <x:v>54174015.5823021</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0605997927634006</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>114.9740401947342</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>54159969.71659391</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>14045.865708194673</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0002593403538018</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00025934035380177113</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1450.2240399141</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.2335306788884437</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>17.121061168933878</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1450.2240399141</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>17.872133444209794</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$233,A7,'Species'!$U$2:$U$233))</x:f>
-        <x:v>25918.59756534583</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.2335306788884437</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>17.121061168933878</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>24829.374496027714</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1089.2230693181154</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0438683249750158</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0438683249750159</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>276079.24405947706</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.359610137929123</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>228.88120851965814</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>276079.24405947706</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>294.82160858102026</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$233,A8,'Species'!$U$2:$U$233))</x:f>
-        <x:v>81394126.8294471</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.359610137929123</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>228.88120851965814</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>63189351.02752676</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>18204775.801920347</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.288098793639927</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.2880987936399271</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>144518.82789510884</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.852741077729534</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>712.4281605433364</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>144518.82789510884</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>847.0950991823489</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$233,A9,'Species'!$U$2:$U$233))</x:f>
-        <x:v>122421190.84952404</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.852741077729534</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>712.4281605433364</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>102959282.7211914</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>19461908.12833263</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1890252885797048</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1890252885797049</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>124.7996995313</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>124.7996995313</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$233,A10,'Species'!$U$2:$U$233))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>52025.173800896155</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>52025.173800896155</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4605.383882439899</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.6952248734667688</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>495.7067965321967</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4605.383882439899</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>541.351146146738</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$233,A11,'Species'!$U$2:$U$233))</x:f>
-        <x:v>2493129.8432045532</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.6952248734667688</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>495.7067965321967</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2282920.091165293</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>210209.75203926023</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0920793298253206</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0920793298253207</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>10030.8278585451</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.990616947263893</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>978.6264448401995</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>10030.8278585451</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1190.381669594843</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$233,A12,'Species'!$U$2:$U$233))</x:f>
-        <x:v>11940513.613673382</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.990616947263893</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>978.6264448401995</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>9816433.406012023</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>2124080.2076613586</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2163800353762373</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.21638003537623726</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>12221.0989887337</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.3482115298959805</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2229.520807712349</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>12221.0989887337</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2339.907271707848</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$233,A13,'Species'!$U$2:$U$233))</x:f>
-        <x:v>28596238.391999412</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.3482115298959805</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2229.520807712349</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>27247194.488494128</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1349043.9035052843</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0495112957069748</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.04951129570697471</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72d47d46b3344bde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b78d11cd4bb417b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16986,20 +16466,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -17007,1362 +16477,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>42858.6115259506</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.713029269903475</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>516.4511750715614</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>42858.6115259506</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>601.0366152601903</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$233,A2,'Species'!$U$2:$U$233))</x:f>
-        <x:v>25759594.806308724</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.713029269903475</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>516.4511750715614</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>22134380.284512747</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3625214.521795977</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1637820655106623</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.1637820655106622</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>762.9680400118</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8346675639603935</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>683.3883390319003</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>762.9680400118</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>706.9452717376557</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$233,A3,'Species'!$U$2:$U$233))</x:f>
-        <x:v>539376.6483732886</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8346675639603935</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>683.3883390319003</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>521403.46159808844</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>17973.186775200127</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0344707852918982</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.03447078529189807</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>13.592053438699999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>13.592053438699999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$233,A4,'Species'!$U$2:$U$233))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>29736.172903859402</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>29736.172903859402</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>6333.561689155298</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.362767269183546</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2305.511374404977</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>6333.561689155298</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2361.3396415748516</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$233,A5,'Species'!$U$2:$U$233))</x:f>
-        <x:v>14955690.288962184</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.362767269183546</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2305.511374404977</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>14602098.514843138</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>353591.7741190456</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.024215134130181</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.024215134130181153</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>8410.887210943598</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.251321722858008</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1783.699632586929</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>8410.887210943598</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1960.6510324045462</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$233,A6,'Species'!$U$2:$U$233))</x:f>
-        <x:v>16490814.69357476</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.251321722858008</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1783.699632586929</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>15002496.427890196</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1488318.2656845637</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0992047072191082</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0992047072191082</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>13594.325604864402</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.327959253583874</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2127.9393888950995</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>13594.325604864402</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2196.3128115392515</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$233,A7,'Species'!$U$2:$U$233))</x:f>
-        <x:v>29857391.490199767</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.327959253583874</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2127.9393888950995</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>28927900.920056157</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>929490.5701436102</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0321312829683809</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.032131282968380886</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>869.4512417498001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3657742454729105</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>232.1529707379111</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>869.4512417498001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>235.0392557106422</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$233,A8,'Species'!$U$2:$U$233))</x:f>
-        <x:v>204355.17273756667</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3657742454729105</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>232.1529707379111</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>201845.6886839818</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2509.4840535848634</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0124326859292685</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.012432685929268564</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1457.7170045951</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9346726558921157</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>860.3450332785393</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1457.7170045951</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>889.1913047019699</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$233,A9,'Species'!$U$2:$U$233))</x:f>
-        <x:v>1296189.2852021644</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9346726558921157</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>860.3450332785393</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1254139.5848290639</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>42049.70037310058</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0335287242997213</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.03352872429972127</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5997.1000611103</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.17715312815355</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1503.672053269652</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5997.1000611103</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1614.3507670987133</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$233,A10,'Species'!$U$2:$U$233))</x:f>
-        <x:v>9681423.084021153</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.17715312815355</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1503.672053269652</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>9017671.76255328</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>663751.3214678727</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.073605620047534</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.07360562004753397</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5155.330244896599</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.1410899079880963</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>138.38528356311252</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5155.330244896599</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>139.1472122788946</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$233,A11,'Species'!$U$2:$U$233))</x:f>
-        <x:v>717349.8319544328</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.1410899079880963</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>138.38528356311252</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>713421.8378015062</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>3927.994152926607</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.005505850739068</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.005505850739067907</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2155.8078773891993</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.67276449704258</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>470.72200082827914</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2155.8078773891993</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>789.1154245364048</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$233,A12,'Species'!$U$2:$U$233))</x:f>
-        <x:v>1701181.2483849039</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.67276449704258</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>470.72200082827914</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1014786.1974460094</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>686395.0509388945</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.6763937592631806</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.6763937592631806</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>456.90392098959995</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>456.90392098959995</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174134</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$233,A13,'Species'!$U$2:$U$233))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>549319.3342430406</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>549319.3342430406</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>12677.852933733499</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.5768703007924585</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>377.4594482949793</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>12677.852933733499</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>602.9005315187958</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$233,A14,'Species'!$U$2:$U$233))</x:f>
-        <x:v>7643484.272265051</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.5768703007924585</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>377.4594482949793</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4785375.373931931</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2858108.898333119</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.5972590810540193</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.5972590810540193</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>235953.06465554558</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.298496343354105</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>198.83660688042696</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>235953.06465554558</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>216.29289139572924</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$233,A15,'Species'!$U$2:$U$233))</x:f>
-        <x:v>51034970.588031396</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.298496343354105</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>198.83660688042696</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>46916106.75914668</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>4118863.8288847134</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0877921062382634</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0877921062382634</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>108969.13540164729</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.886448646864474</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>769.9253991727909</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>108969.13540164729</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>844.3636705034243</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$233,A16,'Species'!$U$2:$U$233))</x:f>
-        <x:v>92009579.13931954</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.886448646864474</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>769.9253991727909</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>83898105.07162718</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>8111474.067692354</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0966824466508185</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.09668244665081843</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>5039.234849608901</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.8214511519206242</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>662.9047820293334</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>5039.234849608901</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>800.0454101000578</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$233,A17,'Species'!$U$2:$U$233))</x:f>
-        <x:v>4031616.711845856</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.8214511519206242</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>662.9047820293334</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>3340532.879574609</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>691083.8322712472</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2068783206705787</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.20687832067057857</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>5203.2774938501</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.3752413343477565</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>23.726918273272116</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>5203.2774938501</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>24.39488142580145</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$233,A18,'Species'!$U$2:$U$233))</x:f>
-        <x:v>126933.33748801451</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.3752413343477565</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>23.726918273272116</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>123457.73984973747</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>3475.597638277046</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0281521243018643</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.02815212430186439</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>3398.043627384</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2030473104600787</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>159.6053005971821</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>3398.043627384</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>167.48889137914867</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$233,A19,'Species'!$U$2:$U$233))</x:f>
-        <x:v>569134.5600085271</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2030473104600787</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>159.6053005971821</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>542345.7745909623</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>26788.785417564795</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0493942917463843</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.04939429174638434</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>1747.6002532578</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.472140660469289</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>296.57918026413114</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>1747.6002532578</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>297.5251804961511</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$233,A20,'Species'!$U$2:$U$233))</x:f>
-        <x:v>519955.0807856463</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.472140660469289</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>296.57918026413114</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>518301.8505405863</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>1653.2302450599964</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0031897054647512</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.003189705464751255</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>478823.95788171655</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0610313989539404</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>115.08835933970904</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>478823.95788171655</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>115.10619459262395</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$233,A21,'Species'!$U$2:$U$233))</x:f>
-        <x:v>55115603.67154324</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0610313989539404</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>115.08835933970904</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>55107063.7251527</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>8539.946390539408</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.000154970085743</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.00015497008574313662</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2.0261533966000003</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2.0261533966000003</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$233,A22,'Species'!$U$2:$U$233))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1088.1087982977872</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>1088.1087982977872</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>4604.1986899041995</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.3968994226799336</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>249.4017076034804</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>4604.1986899041995</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>271.76877148341083</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$233,A23,'Species'!$U$2:$U$233))</x:f>
-        <x:v>1251277.4216207939</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.3968994226799336</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>249.4017076034804</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>1148295.0154078146</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>102982.40621297923</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0896828818649928</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.08968288186499289</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>2174.2613433719002</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.803657647191499</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>636.2937350485039</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>2174.2613433719002</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>644.1862268173651</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$233,A24,'Species'!$U$2:$U$233))</x:f>
-        <x:v>1400629.2109015998</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.803657647191499</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>636.2937350485039</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>1383468.871145684</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>17160.339755915804</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0124038495652634</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.012403849565263374</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>990.0152123130999</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.8200059325944764</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>660.7024733423293</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>990.0152123130999</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>660.7031264547838</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$233,A25,'Species'!$U$2:$U$233))</x:f>
-        <x:v>654106.1460130617</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.8200059325944764</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>660.7024733423293</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>654105.4994217964</x:v>
       </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>0.6465912653366104</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0000009885121985</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>9.885121985798495e-7</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f34f84796b14fd7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf70ec6dce8944627"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18537,7 +17123,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -18636,7 +17222,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>316140800.30548686</x:v>
+        <x:v>273451584.58033705</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18650,7 +17236,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>316140800.3054869</x:v>
+        <x:v>292387446.856549</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18664,7 +17250,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>5.960464477539063e-8</x:v>
+        <x:v>-42689215.72514975</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18678,7 +17264,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-23753353.448937774</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18689,9 +17275,9 @@
         <x:v>EEZ_946</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -18703,47 +17289,19 @@
         <x:v>EEZ_946</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_946</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_946</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re883b2079a48494d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdea7a54ba40248dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18790,7 +17348,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
